--- a/Output Data Tables/APAT Outputs/Miscellaneous Tables/2020/Days_Assigned_by_Aircraft_and_Airline_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Miscellaneous Tables/2020/Days_Assigned_by_Aircraft_and_Airline_2020.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="76" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -226,6 +226,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -274,7 +286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -301,7 +313,11 @@
     <col min="22" max="22" width="6.140625" customWidth="true"/>
     <col min="23" max="23" width="8.85546875" customWidth="true"/>
     <col min="24" max="24" width="8.7109375" customWidth="true"/>
-    <col min="25" max="25" width="10.85546875" customWidth="true"/>
+    <col min="25" max="25" width="7.140625" customWidth="true"/>
+    <col min="26" max="26" width="7.140625" customWidth="true"/>
+    <col min="27" max="27" width="6.140625" customWidth="true"/>
+    <col min="28" max="28" width="8.85546875" customWidth="true"/>
+    <col min="29" max="29" width="10.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -380,6 +396,18 @@
       <c r="Y1" s="0" t="s">
         <v>71</v>
       </c>
+      <c r="Z1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -457,6 +485,18 @@
       <c r="Y2" s="0">
         <v>0</v>
       </c>
+      <c r="Z2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -532,6 +572,18 @@
         <v>0</v>
       </c>
       <c r="Y3" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>25310</v>
+      </c>
+      <c r="AC3" s="0">
         <v>25310</v>
       </c>
     </row>
@@ -609,6 +661,18 @@
         <v>0</v>
       </c>
       <c r="Y4" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>48310</v>
+      </c>
+      <c r="AC4" s="0">
         <v>48310</v>
       </c>
     </row>
@@ -686,6 +750,18 @@
         <v>66020</v>
       </c>
       <c r="Y5" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>84720</v>
+      </c>
+      <c r="AC5" s="0">
         <v>84720</v>
       </c>
     </row>
@@ -763,6 +839,18 @@
         <v>0</v>
       </c>
       <c r="Y6" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>21960</v>
+      </c>
+      <c r="AC6" s="0">
         <v>21960</v>
       </c>
     </row>
@@ -840,6 +928,18 @@
         <v>37400</v>
       </c>
       <c r="Y7" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>203130</v>
+      </c>
+      <c r="AC7" s="0">
         <v>203130</v>
       </c>
     </row>
@@ -919,6 +1019,18 @@
       <c r="Y8" s="0">
         <v>0</v>
       </c>
+      <c r="Z8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -996,6 +1108,18 @@
       <c r="Y9" s="0">
         <v>0</v>
       </c>
+      <c r="Z9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
@@ -1073,6 +1197,18 @@
       <c r="Y10" s="0">
         <v>0</v>
       </c>
+      <c r="Z10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
@@ -1148,6 +1284,18 @@
         <v>0</v>
       </c>
       <c r="Y11" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>10710</v>
+      </c>
+      <c r="AC11" s="0">
         <v>10710</v>
       </c>
     </row>
@@ -1225,6 +1373,18 @@
         <v>0</v>
       </c>
       <c r="Y12" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="0">
+        <v>13610</v>
+      </c>
+      <c r="AC12" s="0">
         <v>13610</v>
       </c>
     </row>
@@ -1302,6 +1462,18 @@
         <v>31080</v>
       </c>
       <c r="Y13" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>64150</v>
+      </c>
+      <c r="AC13" s="0">
         <v>64150</v>
       </c>
     </row>
@@ -1379,6 +1551,18 @@
         <v>0</v>
       </c>
       <c r="Y14" s="0">
+        <v>1360</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>22020</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="0">
         <v>23380</v>
       </c>
     </row>
@@ -1456,6 +1640,18 @@
         <v>13070</v>
       </c>
       <c r="Y15" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>93910</v>
+      </c>
+      <c r="AC15" s="0">
         <v>93910</v>
       </c>
     </row>
@@ -1535,6 +1731,18 @@
       <c r="Y16" s="0">
         <v>11700</v>
       </c>
+      <c r="Z16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>11700</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -1612,6 +1820,18 @@
       <c r="Y17" s="0">
         <v>270</v>
       </c>
+      <c r="Z17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>270</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -1687,6 +1907,18 @@
         <v>0</v>
       </c>
       <c r="Y18" s="0">
+        <v>93150</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>870</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>23080</v>
+      </c>
+      <c r="AB18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="0">
         <v>117100</v>
       </c>
     </row>
@@ -1764,6 +1996,18 @@
         <v>0</v>
       </c>
       <c r="Y19" s="0">
+        <v>65190</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>57480</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>51230</v>
+      </c>
+      <c r="AB19" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="0">
         <v>173900</v>
       </c>
     </row>
@@ -1841,6 +2085,18 @@
         <v>0</v>
       </c>
       <c r="Y20" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>31880</v>
+      </c>
+      <c r="AB20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="0">
         <v>31880</v>
       </c>
     </row>
@@ -1918,6 +2174,18 @@
         <v>0</v>
       </c>
       <c r="Y21" s="0">
+        <v>103940</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>26760</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>15090</v>
+      </c>
+      <c r="AB21" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="0">
         <v>145790</v>
       </c>
     </row>
@@ -1995,6 +2263,18 @@
         <v>0</v>
       </c>
       <c r="Y22" s="0">
+        <v>6150</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>9830</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="0">
         <v>15980</v>
       </c>
     </row>
@@ -2074,6 +2354,18 @@
       <c r="Y23" s="0">
         <v>5670</v>
       </c>
+      <c r="Z23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="0">
+        <v>5670</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
@@ -2151,6 +2443,18 @@
       <c r="Y24" s="0">
         <v>4170</v>
       </c>
+      <c r="Z24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="0">
+        <v>4170</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
@@ -2226,6 +2530,18 @@
         <v>0</v>
       </c>
       <c r="Y25" s="0">
+        <v>29220</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>7060</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="0">
         <v>36280</v>
       </c>
     </row>
@@ -2305,6 +2621,18 @@
       <c r="Y26" s="0">
         <v>0</v>
       </c>
+      <c r="Z26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
@@ -2382,6 +2710,18 @@
       <c r="Y27" s="0">
         <v>0</v>
       </c>
+      <c r="Z27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
@@ -2459,6 +2799,18 @@
       <c r="Y28" s="0">
         <v>0</v>
       </c>
+      <c r="Z28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
@@ -2534,6 +2886,18 @@
         <v>0</v>
       </c>
       <c r="Y29" s="0">
+        <v>19150</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>185810</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>180</v>
+      </c>
+      <c r="AB29" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="0">
         <v>205140</v>
       </c>
     </row>
@@ -2611,6 +2975,18 @@
         <v>0</v>
       </c>
       <c r="Y30" s="0">
+        <v>157180</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>87470</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>12260</v>
+      </c>
+      <c r="AB30" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="0">
         <v>256910</v>
       </c>
     </row>
@@ -2688,6 +3064,18 @@
         <v>0</v>
       </c>
       <c r="Y31" s="0">
+        <v>570</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>12500</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="0">
         <v>13070</v>
       </c>
     </row>
@@ -2765,6 +3153,18 @@
         <v>0</v>
       </c>
       <c r="Y32" s="0">
+        <v>2180</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>2130</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="0">
         <v>4310</v>
       </c>
     </row>
@@ -2842,6 +3242,18 @@
         <v>0</v>
       </c>
       <c r="Y33" s="0">
+        <v>96590</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>24620</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="0">
         <v>121210</v>
       </c>
     </row>
@@ -2921,6 +3333,18 @@
       <c r="Y34" s="0">
         <v>0</v>
       </c>
+      <c r="Z34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -2963,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="0">
-        <v>0</v>
+        <v>18110</v>
       </c>
       <c r="O35" s="0">
         <v>0</v>
@@ -2996,7 +3420,19 @@
         <v>0</v>
       </c>
       <c r="Y35" s="0">
-        <v>0</v>
+        <v>56370</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="0">
+        <v>56370</v>
       </c>
     </row>
     <row r="36">
@@ -3075,6 +3511,18 @@
       <c r="Y36" s="0">
         <v>13450</v>
       </c>
+      <c r="Z36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="0">
+        <v>13450</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
@@ -3152,6 +3600,18 @@
       <c r="Y37" s="0">
         <v>31960</v>
       </c>
+      <c r="Z37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="0">
+        <v>31960</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
@@ -3194,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="0">
-        <v>0</v>
+        <v>2920</v>
       </c>
       <c r="O38" s="0">
         <v>0</v>
@@ -3227,7 +3687,19 @@
         <v>0</v>
       </c>
       <c r="Y38" s="0">
-        <v>0</v>
+        <v>10480</v>
+      </c>
+      <c r="Z38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="0">
+        <v>10480</v>
       </c>
     </row>
     <row r="39">
@@ -3304,6 +3776,18 @@
         <v>0</v>
       </c>
       <c r="Y39" s="0">
+        <v>4960</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>8760</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="0">
         <v>13720</v>
       </c>
     </row>
@@ -3383,6 +3867,18 @@
       <c r="Y40" s="0">
         <v>11700</v>
       </c>
+      <c r="Z40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="0">
+        <v>11700</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
@@ -3460,6 +3956,18 @@
       <c r="Y41" s="0">
         <v>2100</v>
       </c>
+      <c r="Z41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="0">
+        <v>2100</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
@@ -3537,6 +4045,18 @@
       <c r="Y42" s="0">
         <v>4920</v>
       </c>
+      <c r="Z42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="0">
+        <v>4920</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
@@ -3614,6 +4134,18 @@
       <c r="Y43" s="0">
         <v>10230</v>
       </c>
+      <c r="Z43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="0">
+        <v>10230</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
@@ -3691,6 +4223,18 @@
       <c r="Y44" s="0">
         <v>17300</v>
       </c>
+      <c r="Z44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="0">
+        <v>17300</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
@@ -3768,6 +4312,18 @@
       <c r="Y45" s="0">
         <v>4630</v>
       </c>
+      <c r="Z45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="0">
+        <v>4630</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
@@ -3845,6 +4401,18 @@
       <c r="Y46" s="0">
         <v>40540</v>
       </c>
+      <c r="Z46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="0">
+        <v>40540</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
@@ -3922,6 +4490,18 @@
       <c r="Y47" s="0">
         <v>12550</v>
       </c>
+      <c r="Z47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="0">
+        <v>12550</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -3964,7 +4544,7 @@
         <v>12440</v>
       </c>
       <c r="N48" s="0">
-        <v>0</v>
+        <v>284630</v>
       </c>
       <c r="O48" s="0">
         <v>3710</v>
@@ -3997,7 +4577,19 @@
         <v>147570</v>
       </c>
       <c r="Y48" s="0">
-        <v>0</v>
+        <v>817680</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>445310</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>133720</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>565810</v>
+      </c>
+      <c r="AC48" s="0">
+        <v>1962520</v>
       </c>
     </row>
   </sheetData>
